--- a/cotacoes/2026-09-08/fechamento/PEDIDO_CENTROFARMA_09-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/PEDIDO_CENTROFARMA_09-09-2026.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.6% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +5.6% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.6% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +5.6% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -888,28 +888,28 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>655521</v>
+        <v>46141</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>559</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>7899811100596</t>
+          <t>7898060132518</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>BASILICAO POMADA BISNAGA 27G BASILIFLAM</t>
+          <t>AZITROMICINA 500MG CX 5 COMP</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>15.63</v>
+        <v>6.17</v>
       </c>
       <c r="I7" s="5">
         <f>G7*H7</f>
@@ -933,13 +933,13 @@
         <v/>
       </c>
       <c r="K7" s="5" t="n">
-        <v>14.62</v>
+        <v>5.86</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>14.62</v>
+        <v>5.86</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>14.62</v>
+        <v>5.86</v>
       </c>
       <c r="N7" s="6">
         <f>J7/M7-1</f>
@@ -951,7 +951,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.9% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
@@ -1014,41 +1014,41 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>337401</v>
+        <v>664091</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>7897917000031</t>
+          <t>7894913002083</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>BELMIRAX 100MG CX 6 COMP</t>
+          <t>CENTROLIV HOMEM + 50 C/30 CPR</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>2.54</v>
+        <v>36.84</v>
       </c>
       <c r="I9" s="5">
         <f>G9*H9</f>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="K9" s="5" t="n">
-        <v>2.41</v>
+        <v>41.76</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>1.55</v>
+        <v>41.76</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>2.123333333333334</v>
+        <v>41.76</v>
       </c>
       <c r="N9" s="6">
         <f>J9/M9-1</f>
@@ -1077,41 +1077,41 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.4% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>664091</v>
+        <v>31303</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>7894913002083</t>
+          <t>7896658049132</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>CENTROLIV HOMEM + 50 C/30 CPR</t>
+          <t>CIPROFIBRATO 100MG CX 60 COMP</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>36.84</v>
+        <v>26.34</v>
       </c>
       <c r="I10" s="5">
         <f>G10*H10</f>
@@ -1122,13 +1122,13 @@
         <v/>
       </c>
       <c r="K10" s="5" t="n">
-        <v>41.76</v>
+        <v>28.9</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>41.76</v>
+        <v>28.9</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>41.76</v>
+        <v>28.9</v>
       </c>
       <c r="N10" s="6">
         <f>J10/M10-1</f>
@@ -1140,41 +1140,41 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>31303</v>
+        <v>136261</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1588</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>7896658049132</t>
+          <t>7898060131399</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>CIPROFIBRATO 100MG CX 60 COMP</t>
+          <t>CLORIDRATO DE CIPROFLOXACINO 500MG CX 14 COMP REV</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>26.34</v>
+        <v>6.31</v>
       </c>
       <c r="I11" s="5">
         <f>G11*H11</f>
@@ -1185,13 +1185,13 @@
         <v/>
       </c>
       <c r="K11" s="5" t="n">
-        <v>28.9</v>
+        <v>5.99</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>28.9</v>
+        <v>5.99</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>28.9</v>
+        <v>5.989999999999999</v>
       </c>
       <c r="N11" s="6">
         <f>J11/M11-1</f>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
@@ -1392,41 +1392,41 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>201981</v>
+        <v>597721</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>7897917000161</t>
+          <t>7898920041455</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>DELTAPIL 0,20MG LOCAO FR 100ML</t>
+          <t>CREATINE MAX TITANIUM 150G</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>8.119999999999999</v>
+        <v>28.79</v>
       </c>
       <c r="I15" s="5">
         <f>G15*H15</f>
@@ -1437,13 +1437,13 @@
         <v/>
       </c>
       <c r="K15" s="5" t="n">
-        <v>8.220000000000001</v>
+        <v>27.35</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>8.220000000000001</v>
+        <v>27.35</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>8.220000000000001</v>
+        <v>27.35</v>
       </c>
       <c r="N15" s="6">
         <f>J15/M15-1</f>
@@ -1455,28 +1455,28 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>649041</v>
+        <v>201981</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>7896902208612</t>
+          <t>7897917000161</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DESCOL FARMAX 8G CAMOMILA P/CABELOS</t>
+          <t>DELTAPIL 0,20MG LOCAO FR 100ML</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1489,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>2.37</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="I16" s="5">
         <f>G16*H16</f>
@@ -1500,13 +1500,13 @@
         <v/>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.31</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>2.31</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>2.31</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N16" s="6">
         <f>J16/M16-1</f>
@@ -1518,41 +1518,41 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>642951</v>
+        <v>649041</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>7894913003745</t>
+          <t>7896902208612</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>EXOMUC ADULTO MEL/LIMAO 120ML</t>
+          <t>DESCOL FARMAX 8G CAMOMILA P/CABELOS</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>13.82</v>
+        <v>2.37</v>
       </c>
       <c r="I17" s="5">
         <f>G17*H17</f>
@@ -1563,13 +1563,13 @@
         <v/>
       </c>
       <c r="K17" s="5" t="n">
-        <v>16.33</v>
+        <v>2.31</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>16.33</v>
+        <v>2.31</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>16.33</v>
+        <v>2.31</v>
       </c>
       <c r="N17" s="6">
         <f>J17/M17-1</f>
@@ -1581,41 +1581,41 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>642961</v>
+        <v>638511</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>7894913002922</t>
+          <t>7896902208599</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>F GARENA 180ML</t>
+          <t>DESCOL FARMAX 8G QUERATIN P/CABELOS</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>15.49</v>
+        <v>2.37</v>
       </c>
       <c r="I18" s="5">
         <f>G18*H18</f>
@@ -1626,13 +1626,13 @@
         <v/>
       </c>
       <c r="K18" s="5" t="n">
-        <v>16.6</v>
+        <v>2.25</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>16.6</v>
+        <v>2.25</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>16.6</v>
+        <v>2.25</v>
       </c>
       <c r="N18" s="6">
         <f>J18/M18-1</f>
@@ -1644,32 +1644,32 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>626071</v>
+        <v>642951</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>7896023756849</t>
+          <t>7894913003745</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>FIGATIL 10ML FLACONETE</t>
+          <t>EXOMUC ADULTO MEL/LIMAO 120ML</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>1</v>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>94.06</v>
+        <v>13.82</v>
       </c>
       <c r="I19" s="5">
         <f>G19*H19</f>
@@ -1689,13 +1689,13 @@
         <v/>
       </c>
       <c r="K19" s="5" t="n">
-        <v>2.4223</v>
+        <v>16.33</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>1.1388</v>
+        <v>16.33</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>1.994466666666667</v>
+        <v>16.33</v>
       </c>
       <c r="N19" s="6">
         <f>J19/M19-1</f>
@@ -1710,29 +1710,25 @@
           <t>OK (≤ últ. compra)</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1 emb = 48 un</t>
-        </is>
-      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>616141</v>
+        <v>642961</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>7899838832012</t>
+          <t>7894913002922</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>FITA DE KINESIO 5CM X 5M VERMELHA</t>
+          <t>F GARENA 180ML</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1745,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>19.67</v>
+        <v>15.49</v>
       </c>
       <c r="I20" s="5">
         <f>G20*H20</f>
@@ -1756,13 +1752,13 @@
         <v/>
       </c>
       <c r="K20" s="5" t="n">
-        <v>18.69</v>
+        <v>16.6</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>18.69</v>
+        <v>16.6</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>18.69</v>
+        <v>16.6</v>
       </c>
       <c r="N20" s="6">
         <f>J20/M20-1</f>
@@ -1774,32 +1770,32 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.2% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>638781</v>
+        <v>626071</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>040141785435</t>
+          <t>7896023756849</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>FORTMAGRI 1500MG 60 CPS (BERBERINA+FENO+MOROSIL+CROMO)</t>
+          <t>FIGATIL 10ML FLACONETE</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>1</v>
@@ -1808,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>64.67</v>
+        <v>94.06</v>
       </c>
       <c r="I21" s="5">
         <f>G21*H21</f>
@@ -1819,13 +1815,13 @@
         <v/>
       </c>
       <c r="K21" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>2.4223</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>1.1388</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>79.90000000000001</v>
+        <v>1.994466666666667</v>
       </c>
       <c r="N21" s="6">
         <f>J21/M21-1</f>
@@ -1837,28 +1833,32 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>1 emb = 48 un</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>619931</v>
+        <v>616141</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>7894913002809</t>
+          <t>7899838832012</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>GLUCOZINC LARANJA 120ML</t>
+          <t>FITA DE KINESIO 5CM X 5M VERMELHA</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>16.67</v>
+        <v>19.67</v>
       </c>
       <c r="I22" s="5">
         <f>G22*H22</f>
@@ -1882,13 +1882,13 @@
         <v/>
       </c>
       <c r="K22" s="5" t="n">
-        <v>17.61</v>
+        <v>18.69</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>17.61</v>
+        <v>18.69</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>17.61</v>
+        <v>18.69</v>
       </c>
       <c r="N22" s="6">
         <f>J22/M22-1</f>
@@ -1900,41 +1900,41 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.2% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>276061</v>
+        <v>638781</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>8902220114128</t>
+          <t>040141785435</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>HEMIFUMARATO DE BISOPROLOL 1,25MG CX 30 COMP REV</t>
+          <t>FORTMAGRI 1500MG 60 CPS (BERBERINA+FENO+MOROSIL+CROMO)</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>11.81</v>
+        <v>64.67</v>
       </c>
       <c r="I23" s="5">
         <f>G23*H23</f>
@@ -1945,13 +1945,13 @@
         <v/>
       </c>
       <c r="K23" s="5" t="n">
-        <v>19.81</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>19.81</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>19.81</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="N23" s="6">
         <f>J23/M23-1</f>
@@ -1963,28 +1963,28 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>597601</v>
+        <v>619931</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>7899941201958</t>
+          <t>7894913002809</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>HORUS MAX TITANIUM BLUE ICE POTE 150G</t>
+          <t>GLUCOZINC LARANJA 120ML</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -1997,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>41.64</v>
+        <v>16.67</v>
       </c>
       <c r="I24" s="5">
         <f>G24*H24</f>
@@ -2008,13 +2008,13 @@
         <v/>
       </c>
       <c r="K24" s="5" t="n">
-        <v>63.43</v>
+        <v>17.61</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>63.43</v>
+        <v>17.61</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>63.43</v>
+        <v>17.61</v>
       </c>
       <c r="N24" s="6">
         <f>J24/M24-1</f>
@@ -2026,41 +2026,41 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>597591</v>
+        <v>276061</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>7899941202849</t>
+          <t>8902220114128</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>HORUS MAX TITANIUM CITRUS POTE 150G</t>
+          <t>HEMIFUMARATO DE BISOPROLOL 1,25MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>41.64</v>
+        <v>11.81</v>
       </c>
       <c r="I25" s="5">
         <f>G25*H25</f>
@@ -2071,13 +2071,13 @@
         <v/>
       </c>
       <c r="K25" s="5" t="n">
-        <v>56.83</v>
+        <v>19.81</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>56.83</v>
+        <v>19.81</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>56.83000000000001</v>
+        <v>19.81</v>
       </c>
       <c r="N25" s="6">
         <f>J25/M25-1</f>
@@ -2089,41 +2089,41 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>56761</v>
+        <v>276001</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>9752</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>7898060132075</t>
+          <t>8902220114166</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MAL DEXCLORFENIRAMINA+BETAMETASONA 0,4+0,05MG XPE FR 120ML+CM</t>
+          <t>HEMIFUMARATO DE BISOPROLOL 2,5MG CX 30 COMP REV</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>4.65</v>
+        <v>7.29</v>
       </c>
       <c r="I26" s="5">
         <f>G26*H26</f>
@@ -2134,13 +2134,13 @@
         <v/>
       </c>
       <c r="K26" s="5" t="n">
-        <v>5.1</v>
+        <v>6.92</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>5.1</v>
+        <v>6.92</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>5.1</v>
+        <v>6.919999999999999</v>
       </c>
       <c r="N26" s="6">
         <f>J26/M26-1</f>
@@ -2152,41 +2152,41 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>334801</v>
+        <v>597601</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>7897917005180</t>
+          <t>7899941201958</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MALEATO DE ENALAPRIL 5MG CX 30 COMP</t>
+          <t>HORUS MAX TITANIUM BLUE ICE POTE 150G</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>2</v>
+        <v>41.64</v>
       </c>
       <c r="I27" s="5">
         <f>G27*H27</f>
@@ -2197,13 +2197,13 @@
         <v/>
       </c>
       <c r="K27" s="5" t="n">
-        <v>2.18</v>
+        <v>63.43</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>2.18</v>
+        <v>63.43</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>2.18</v>
+        <v>63.43</v>
       </c>
       <c r="N27" s="6">
         <f>J27/M27-1</f>
@@ -2215,28 +2215,28 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>605911</v>
+        <v>597591</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>7896004779201</t>
+          <t>7899941202849</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MARACUJA CONCENTRIX SOL ORAL 100ML (PASS</t>
+          <t>HORUS MAX TITANIUM CITRUS POTE 150G</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -2249,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>12.09</v>
+        <v>41.64</v>
       </c>
       <c r="I28" s="5">
         <f>G28*H28</f>
@@ -2260,13 +2260,13 @@
         <v/>
       </c>
       <c r="K28" s="5" t="n">
-        <v>11.9433</v>
+        <v>56.83</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>10.92</v>
+        <v>56.83</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>11.6022</v>
+        <v>56.83000000000001</v>
       </c>
       <c r="N28" s="6">
         <f>J28/M28-1</f>
@@ -2278,41 +2278,41 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.2% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>555821</v>
+        <v>556441</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>7898283815182</t>
+          <t>7897732607323</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MASCARA TRIPLA C/ELASTI BRANCA 50UN CART</t>
+          <t>LEITE DE MAGNESIA 100ML TRADICIONAL</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>8.109999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="I29" s="5">
         <f>G29*H29</f>
@@ -2323,13 +2323,13 @@
         <v/>
       </c>
       <c r="K29" s="5" t="n">
-        <v>9.83</v>
+        <v>4.12</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>9.83</v>
+        <v>4.12</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>9.83</v>
+        <v>4.12</v>
       </c>
       <c r="N29" s="6">
         <f>J29/M29-1</f>
@@ -2341,41 +2341,41 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>598371</v>
+        <v>492281</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>7896902285422</t>
+          <t>7908020500889</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>OLEO CAP/CORP FARMAX 30ML PURO RICINO</t>
+          <t>LEVONORGESTREL 0,15+0,03MG CX 21 COMP REV+CALEND</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>4.61</v>
+        <v>3.4</v>
       </c>
       <c r="I30" s="5">
         <f>G30*H30</f>
@@ -2386,13 +2386,13 @@
         <v/>
       </c>
       <c r="K30" s="5" t="n">
-        <v>4.69</v>
+        <v>3.23</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>4.69</v>
+        <v>3.23</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>4.69</v>
+        <v>3.23</v>
       </c>
       <c r="N30" s="6">
         <f>J30/M30-1</f>
@@ -2404,41 +2404,41 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>274781</v>
+        <v>56761</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>7898100243112</t>
+          <t>7898060132075</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>PHITOSS 7MG/ML XPE FR 100ML PET</t>
+          <t>MAL DEXCLORFENIRAMINA+BETAMETASONA 0,4+0,05MG XPE FR 120ML+CM</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>5.67</v>
+        <v>4.65</v>
       </c>
       <c r="I31" s="5">
         <f>G31*H31</f>
@@ -2449,13 +2449,13 @@
         <v/>
       </c>
       <c r="K31" s="5" t="n">
-        <v>5.49</v>
+        <v>5.1</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>5.49</v>
+        <v>5.1</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>5.489999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="N31" s="6">
         <f>J31/M31-1</f>
@@ -2467,41 +2467,41 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.3% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>393141</v>
+        <v>334801</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>7896004755410</t>
+          <t>7897917005180</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>PRAZY 20MG CX 4BL X 7 COMP REV</t>
+          <t>MALEATO DE ENALAPRIL 5MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>7.16</v>
       </c>
       <c r="I32" s="5">
         <f>G32*H32</f>
@@ -2512,13 +2512,13 @@
         <v/>
       </c>
       <c r="K32" s="5" t="n">
-        <v>6.8</v>
+        <v>2.18</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>6.6</v>
+        <v>2.18</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>6.733333333333333</v>
+        <v>2.18</v>
       </c>
       <c r="N32" s="6">
         <f>J32/M32-1</f>
@@ -2530,41 +2530,41 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.3% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>408041</v>
+        <v>605911</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>7898569765514</t>
+          <t>7896004779201</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>PREDNISOLONA 40MG CX 7 COMP</t>
+          <t>MARACUJA CONCENTRIX SOL ORAL 100ML (PASS</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>10.4</v>
+        <v>12.09</v>
       </c>
       <c r="I33" s="5">
         <f>G33*H33</f>
@@ -2575,13 +2575,13 @@
         <v/>
       </c>
       <c r="K33" s="5" t="n">
-        <v>9.75</v>
+        <v>11.9433</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>9.75</v>
+        <v>10.92</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>9.75</v>
+        <v>11.6022</v>
       </c>
       <c r="N33" s="6">
         <f>J33/M33-1</f>
@@ -2593,41 +2593,41 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.7% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +1.2% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>657361</v>
+        <v>555821</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>7898079003168</t>
+          <t>7898283815182</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>PRES. PRUDENCE LUBRIFICADOS LEVE8 PAGUE6</t>
+          <t>MASCARA TRIPLA C/ELASTI BRANCA 50UN CART</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>6.94</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I34" s="5">
         <f>G34*H34</f>
@@ -2638,13 +2638,13 @@
         <v/>
       </c>
       <c r="K34" s="5" t="n">
-        <v>6.88</v>
+        <v>9.83</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>6.67</v>
+        <v>9.83</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>6.739999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="N34" s="6">
         <f>J34/M34-1</f>
@@ -2656,28 +2656,28 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.9% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>632781</v>
+        <v>643061</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>7896007202720</t>
+          <t>7894913003691</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>PRESERV BLOWTEX SENS EXTRA FINO 3UN</t>
+          <t>NINNAR MELATONINA 120CPR MARACUJA</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -2690,7 +2690,7 @@
         <v>3</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>8.1</v>
+        <v>17.78</v>
       </c>
       <c r="I35" s="5">
         <f>G35*H35</f>
@@ -2701,13 +2701,13 @@
         <v/>
       </c>
       <c r="K35" s="5" t="n">
-        <v>7.79</v>
+        <v>16.84</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>7.16</v>
+        <v>16.84</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>7.580000000000001</v>
+        <v>16.84</v>
       </c>
       <c r="N35" s="6">
         <f>J35/M35-1</f>
@@ -2719,28 +2719,28 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.0% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +5.6% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>595621</v>
+        <v>643071</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>7898079000358</t>
+          <t>7894913003189</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>PRESERV PRUDENCE T FRUTTI 12UN</t>
+          <t>NINNAR MELATONINA MARACUJA 30ML</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>4.18</v>
+        <v>13.79</v>
       </c>
       <c r="I36" s="5">
         <f>G36*H36</f>
@@ -2764,13 +2764,13 @@
         <v/>
       </c>
       <c r="K36" s="5" t="n">
-        <v>5.13</v>
+        <v>13.1</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>4.97</v>
+        <v>13.1</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>4.976666666666667</v>
+        <v>13.1</v>
       </c>
       <c r="N36" s="6">
         <f>J36/M36-1</f>
@@ -2782,41 +2782,41 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>595611</v>
+        <v>598371</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>7898079002963</t>
+          <t>7896902285422</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>PRESERV PRUDENCE ULT S 6X8 OF</t>
+          <t>OLEO CAP/CORP FARMAX 30ML PURO RICINO</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>10.52</v>
+        <v>4.61</v>
       </c>
       <c r="I37" s="5">
         <f>G37*H37</f>
@@ -2827,13 +2827,13 @@
         <v/>
       </c>
       <c r="K37" s="5" t="n">
-        <v>9.99</v>
+        <v>4.69</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>9.69</v>
+        <v>4.69</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>9.69</v>
+        <v>4.69</v>
       </c>
       <c r="N37" s="6">
         <f>J37/M37-1</f>
@@ -2845,41 +2845,41 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.3% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>585321</v>
+        <v>274781</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>7898079003021</t>
+          <t>7898100243112</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>PRESERV. PRUDENCE LUB.12X3</t>
+          <t>PHITOSS 7MG/ML XPE FR 100ML PET</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>3.93</v>
+        <v>5.67</v>
       </c>
       <c r="I38" s="5">
         <f>G38*H38</f>
@@ -2890,13 +2890,13 @@
         <v/>
       </c>
       <c r="K38" s="5" t="n">
-        <v>3.91</v>
+        <v>5.49</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>3.91</v>
+        <v>5.49</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>3.91</v>
+        <v>5.489999999999999</v>
       </c>
       <c r="N38" s="6">
         <f>J38/M38-1</f>
@@ -2908,28 +2908,28 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +0.5% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +3.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>585341</v>
+        <v>657361</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>7898079000495</t>
+          <t>7898079003168</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PRESERV. PRUDENCE MELANCIA 12X3</t>
+          <t>PRES. PRUDENCE LUBRIFICADOS LEVE8 PAGUE6</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -2942,7 +2942,7 @@
         <v>7</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>4.76</v>
+        <v>6.94</v>
       </c>
       <c r="I39" s="5">
         <f>G39*H39</f>
@@ -2953,13 +2953,13 @@
         <v/>
       </c>
       <c r="K39" s="5" t="n">
-        <v>5.5</v>
+        <v>6.88</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>5.5</v>
+        <v>6.67</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>5.5</v>
+        <v>6.739999999999999</v>
       </c>
       <c r="N39" s="6">
         <f>J39/M39-1</f>
@@ -2971,41 +2971,41 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +0.9% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>585381</v>
+        <v>632781</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>7898079000327</t>
+          <t>7896007202720</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>PRESERV. PRUDENCE UVA 12X3</t>
+          <t>PRESERV BLOWTEX SENS EXTRA FINO 3UN</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>3.8</v>
+        <v>8.1</v>
       </c>
       <c r="I40" s="5">
         <f>G40*H40</f>
@@ -3016,13 +3016,13 @@
         <v/>
       </c>
       <c r="K40" s="5" t="n">
-        <v>5.17</v>
+        <v>7.79</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>5.17</v>
+        <v>7.16</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>5.17</v>
+        <v>7.580000000000001</v>
       </c>
       <c r="N40" s="6">
         <f>J40/M40-1</f>
@@ -3034,28 +3034,28 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +4.0% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>2193</v>
+        <v>595621</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>7896902212497</t>
+          <t>7898079000358</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>REPELENTE BABY FARMAX MOSKITOFF 100ML</t>
+          <t>PRESERV PRUDENCE T FRUTTI 12UN</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
@@ -3068,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>16.83</v>
+        <v>4.18</v>
       </c>
       <c r="I41" s="5">
         <f>G41*H41</f>
@@ -3079,13 +3079,13 @@
         <v/>
       </c>
       <c r="K41" s="5" t="n">
-        <v>20.39</v>
+        <v>5.13</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>20.39</v>
+        <v>4.97</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>20.39</v>
+        <v>4.976666666666667</v>
       </c>
       <c r="N41" s="6">
         <f>J41/M41-1</f>
@@ -3097,41 +3097,41 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>685901</v>
+        <v>585321</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>7898706401930</t>
+          <t>7898079003021</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>SERINGA P/LAVAGEM NASAL LALA JACARE 10ML</t>
+          <t>PRESERV. PRUDENCE LUB.12X3</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>14.17</v>
+        <v>3.93</v>
       </c>
       <c r="I42" s="5">
         <f>G42*H42</f>
@@ -3142,13 +3142,13 @@
         <v/>
       </c>
       <c r="K42" s="5" t="n">
-        <v>14.69</v>
+        <v>3.91</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>13.46</v>
+        <v>3.91</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>13.46</v>
+        <v>3.91</v>
       </c>
       <c r="N42" s="6">
         <f>J42/M42-1</f>
@@ -3160,41 +3160,41 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +0.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>2203</v>
+        <v>585341</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>7894164010844</t>
+          <t>7898079000495</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>SIMETICONA 75MG 10ML GTS</t>
+          <t>PRESERV. PRUDENCE MELANCIA 12X3</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>1.57</v>
+        <v>4.76</v>
       </c>
       <c r="I43" s="5">
         <f>G43*H43</f>
@@ -3205,13 +3205,13 @@
         <v/>
       </c>
       <c r="K43" s="5" t="n">
-        <v>1.78</v>
+        <v>5.5</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>1.77</v>
+        <v>5.5</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>1.77</v>
+        <v>5.5</v>
       </c>
       <c r="N43" s="6">
         <f>J43/M43-1</f>
@@ -3223,41 +3223,41 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>4963</v>
+        <v>585361</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>7894164010899</t>
+          <t>7898079000303</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>SIMETICONA 75MG 15ML GTS</t>
+          <t>PRESERV. PRUDENCE MORANGO 12X3</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>2.31</v>
+        <v>5.18</v>
       </c>
       <c r="I44" s="5">
         <f>G44*H44</f>
@@ -3268,13 +3268,13 @@
         <v/>
       </c>
       <c r="K44" s="5" t="n">
-        <v>2.28</v>
+        <v>4.92</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>2.28</v>
+        <v>4.92</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>2.28</v>
+        <v>4.92</v>
       </c>
       <c r="N44" s="6">
         <f>J44/M44-1</f>
@@ -3286,41 +3286,41 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +1.3% (aceito, lim 5%)</t>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>438221</v>
+        <v>585381</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>7898060138091</t>
+          <t>7898079000327</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>SINVASMAX 40MG CX 30 COMP REV</t>
+          <t>PRESERV. PRUDENCE UVA 12X3</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>5.46</v>
+        <v>3.8</v>
       </c>
       <c r="I45" s="5">
         <f>G45*H45</f>
@@ -3331,13 +3331,13 @@
         <v/>
       </c>
       <c r="K45" s="5" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>5.09</v>
+        <v>5.17</v>
       </c>
       <c r="N45" s="6">
         <f>J45/M45-1</f>
@@ -3349,41 +3349,41 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.3% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>630641</v>
+        <v>2193</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>7894913003738</t>
+          <t>7896902212497</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>UNIQ B12 BAUNILHA C/60 CPR MASTIGAVEL</t>
+          <t>REPELENTE BABY FARMAX MOSKITOFF 100ML</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>19.97</v>
+        <v>16.83</v>
       </c>
       <c r="I46" s="5">
         <f>G46*H46</f>
@@ -3394,13 +3394,13 @@
         <v/>
       </c>
       <c r="K46" s="5" t="n">
-        <v>19.97</v>
+        <v>20.39</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>18.97</v>
+        <v>20.39</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>18.97</v>
+        <v>20.39</v>
       </c>
       <c r="N46" s="6">
         <f>J46/M46-1</f>
@@ -3419,34 +3419,34 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3063</v>
+        <v>671161</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>7898687734089</t>
+          <t>7898706400155</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>VITAMINA D3 15000UI CX 4 CAP</t>
+          <t>SERINGA P/ LAVAGEM NASAL 10ML PATATI PAT</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>13.35</v>
+        <v>15.6</v>
       </c>
       <c r="I47" s="5">
         <f>G47*H47</f>
@@ -3457,13 +3457,13 @@
         <v/>
       </c>
       <c r="K47" s="5" t="n">
-        <v>14.54</v>
+        <v>14.82</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>10.73</v>
+        <v>14.69</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>13.27</v>
+        <v>14.77666666666667</v>
       </c>
       <c r="N47" s="6">
         <f>J47/M47-1</f>
@@ -3475,41 +3475,41 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +5.6% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>193001</v>
+        <v>685901</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>7898569765019</t>
+          <t>7898706401930</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>VITAMINA D3 5000UI CX 30 CAP</t>
+          <t>SERINGA P/LAVAGEM NASAL LALA JACARE 10ML</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>14.04</v>
+        <v>14.17</v>
       </c>
       <c r="I48" s="5">
         <f>G48*H48</f>
@@ -3520,13 +3520,13 @@
         <v/>
       </c>
       <c r="K48" s="5" t="n">
-        <v>13.68</v>
+        <v>14.69</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>13.68</v>
+        <v>13.46</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>13.68</v>
+        <v>13.46</v>
       </c>
       <c r="N48" s="6">
         <f>J48/M48-1</f>
@@ -3538,26 +3538,530 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.6% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="D49" s="7" t="inlineStr">
+      <c r="A49" s="2" t="n">
+        <v>2203</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>8924</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>7894164010844</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>SIMETICONA 75MG 10ML GTS</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I49" s="5">
+        <f>G49*H49</f>
+        <v/>
+      </c>
+      <c r="J49" s="5">
+        <f>H49/E49</f>
+        <v/>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="M49" s="5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N49" s="6">
+        <f>J49/M49-1</f>
+        <v/>
+      </c>
+      <c r="O49" s="6">
+        <f>J49/K49-1</f>
+        <v/>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>4963</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>6131</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>7894164010899</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>SIMETICONA 75MG 15ML GTS</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I50" s="5">
+        <f>G50*H50</f>
+        <v/>
+      </c>
+      <c r="J50" s="5">
+        <f>H50/E50</f>
+        <v/>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M50" s="5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N50" s="6">
+        <f>J50/M50-1</f>
+        <v/>
+      </c>
+      <c r="O50" s="6">
+        <f>J50/K50-1</f>
+        <v/>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>REAJUSTE +1.3% vs últ. (≤4%)</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>591661</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>6485</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>7898108640609</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>TESTE DE GRAVIDEZ CONFIRA</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I51" s="5">
+        <f>G51*H51</f>
+        <v/>
+      </c>
+      <c r="J51" s="5">
+        <f>H51/E51</f>
+        <v/>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M51" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N51" s="6">
+        <f>J51/M51-1</f>
+        <v/>
+      </c>
+      <c r="O51" s="6">
+        <f>J51/K51-1</f>
+        <v/>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>REAJUSTE +5.2% vs média (≤6%)</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>630641</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>6656</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>7894913003738</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>UNIQ B12 BAUNILHA C/60 CPR MASTIGAVEL</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="I52" s="5">
+        <f>G52*H52</f>
+        <v/>
+      </c>
+      <c r="J52" s="5">
+        <f>H52/E52</f>
+        <v/>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="N52" s="6">
+        <f>J52/M52-1</f>
+        <v/>
+      </c>
+      <c r="O52" s="6">
+        <f>J52/K52-1</f>
+        <v/>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>55781</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>7898495603218</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>VENCIDO - DEXTAMINE 2MG+025MG CX 20 COMP</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="I53" s="5">
+        <f>G53*H53</f>
+        <v/>
+      </c>
+      <c r="J53" s="5">
+        <f>H53/E53</f>
+        <v/>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="M53" s="5" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="N53" s="6">
+        <f>J53/M53-1</f>
+        <v/>
+      </c>
+      <c r="O53" s="6">
+        <f>J53/K53-1</f>
+        <v/>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>3063</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>6811</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>7898687734089</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>VITAMINA D3 15000UI CX 4 CAP</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="I54" s="5">
+        <f>G54*H54</f>
+        <v/>
+      </c>
+      <c r="J54" s="5">
+        <f>H54/E54</f>
+        <v/>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="N54" s="6">
+        <f>J54/M54-1</f>
+        <v/>
+      </c>
+      <c r="O54" s="6">
+        <f>J54/K54-1</f>
+        <v/>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>OK (≤ últ. compra)</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>193261</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>6831</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>7898569765194</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>VITAMINA D3 50000UI BL 8 CAP</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="I55" s="5">
+        <f>G55*H55</f>
+        <v/>
+      </c>
+      <c r="J55" s="5">
+        <f>H55/E55</f>
+        <v/>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="M55" s="5" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="N55" s="6">
+        <f>J55/M55-1</f>
+        <v/>
+      </c>
+      <c r="O55" s="6">
+        <f>J55/K55-1</f>
+        <v/>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>REAJUSTE +5.3% vs média (≤6%)</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>193001</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>6824</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>7898569765019</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>VITAMINA D3 5000UI CX 30 CAP</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="I56" s="5">
+        <f>G56*H56</f>
+        <v/>
+      </c>
+      <c r="J56" s="5">
+        <f>H56/E56</f>
+        <v/>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="M56" s="5" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="N56" s="6">
+        <f>J56/M56-1</f>
+        <v/>
+      </c>
+      <c r="O56" s="6">
+        <f>J56/K56-1</f>
+        <v/>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>REAJUSTE +2.6% vs últ. (≤4%)</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I49" s="8">
-        <f>SUM(I2:I48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Pedido FINAL CENTROFARMA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: preço até 5% acima da referência (últ. compra; sem ela, menor histórico), 10% quando o item está zerado. 'Qtd pedido' na embalagem do fornecedor.</t>
+      <c r="I57" s="8">
+        <f>SUM(I2:I56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Pedido FINAL CENTROFARMA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: teto de reajuste de 4% sobre a última compra OU 6% sobre a média histórica (3/6/12m). 'Qtd pedido' na embalagem do fornecedor.</t>
         </is>
       </c>
     </row>
